--- a/backend/Invoice_Log_Highlighted.xlsx
+++ b/backend/Invoice_Log_Highlighted.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -848,6 +848,226 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-07 18:28:05</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>manual_upload</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>unnamed.jpg</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Surabhi Hardwares, Bangalore</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>VTX/992/21</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2021-01-12</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>31360</v>
+      </c>
+      <c r="I13" t="n">
+        <v>6860</v>
+      </c>
+      <c r="J13" t="n">
+        <v>38220</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1sKgwbiwC7D8YW-UmuZoL1vN1e8wPE0HW/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-10 18:36:30</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>manual_upload</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Performa invoice.jpeg</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NovaTech Solutions</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>47200</v>
+      </c>
+      <c r="I14" t="n">
+        <v>7200</v>
+      </c>
+      <c r="J14" t="n">
+        <v>54400</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1lCEGhdOSmfG9UUyLo9Uq9jSispVFQ8Df/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-12 17:42:14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>manual_upload</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>exp10 elayaraji.pdf</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-12T17:42:05.154244</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>75</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>75</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1sFwOVBpLPz5bBd6vYgebGgpfldyZ2X1N/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-17 20:27:09</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>manual_upload</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Hyperion.jpeg</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Hyperion IT Solutions</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>38940</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5940</v>
+      </c>
+      <c r="J16" t="n">
+        <v>44880</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1KxDJQFnfDuoSDcaLaTuVzskcgP87TKdx/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-23 17:26:29</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>manual_upload</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Gemini_Generated_Image_frntndfrntndfrnt.png</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Capella Networks</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>INV-2023-A79</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>4410</v>
+      </c>
+      <c r="I17" t="n">
+        <v>210</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4620</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/13X1kALazAJoUri-fNK34hIamoXrI2DC-/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
